--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2021_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2021_maule.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:28</t>
+    <t xml:space="preserve">2026-09-24 01:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>-0.11</v>
@@ -762,7 +762,7 @@
         <v>0.17</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.07</v>
@@ -782,13 +782,13 @@
         <v>30</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.08</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="13">
@@ -805,10 +805,10 @@
         <v>30</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>-0.1</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2021_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2021_maule.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:18</t>
+    <t xml:space="preserve">2026-10-01 23:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2021_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2021_maule.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:17</t>
+    <t xml:space="preserve">2026-10-05 19:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
